--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_TB.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_TB.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rcad2904ab8af48b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R629edde36ffc495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R2d09421205884fb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R771064e96e534bab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R76e9c0b66b474835"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Raaa9aaddd5814818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R30e1a43e6a7a4896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R4f172c2fd69c4674"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R3d9f78665b884f46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rc56d7f22b08e4785"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R00e49b8ba20942e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rb9bfe9d58f5447ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rf5c58b7ec1ec4f6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rd4747b0b23c74125"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R27f6292b40fe48a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R55e42a65194c4c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Re93e4e6d81f64c27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R0a24d743b2f04953"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rabeea3eec580442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rfac73d6416f541e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rb81748d21fcc489d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rdcf7848959d14613"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R2d9ab0e1a67742c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R43549eb60e29473f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R647186c7c6e340d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R0970f13888df4661"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R0866b8785c9d40e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R13409307a5e0419b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rfdaacae92ea1424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Ra76915a133a74725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rd195ce61a1b341e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rd00c85e6d5fb40c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R9186c042115b4f58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R73f27283d12d45cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R9fe3e61f02c04938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R73129ff0d3094c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R9921b392d243423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rffb38525cefb4bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R027d0913bee74732"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R39e66eeb015343c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R67d0b35958254426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R3ef9347172f842f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Ra2d4fdb008404212"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2948,6 +2949,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>ミョソン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>朝の国・花仙谷</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
